--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101972023</v>
+        <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>5179</v>
+        <v>92353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,58 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S Hultet, Sm</t>
+          <t>Högamålen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578783</v>
+        <v>578809</v>
       </c>
       <c r="R2" t="n">
-        <v>6337436</v>
+        <v>6337402</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>21:45</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>03:00</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,56 +759,55 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Oscar Nordahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Oscar Nordahl, Joakim Holm</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101972023</t>
+          <t>https://artportalen.se/Sighting/137158491</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102353836</v>
+        <v>101972023</v>
       </c>
       <c r="B3" t="n">
-        <v>40267</v>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101166</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,16 +818,20 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>puppa</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Hultet, Sm</t>
@@ -914,11 +886,6 @@
           <t>03:00</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På grov asp-stam i timmerhög. Den yttersta delen av puppan stack ut ur kläckhålet (uttagen på bilden). Fyra ex av grön aspvedbock sprang runt på samma stam.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -943,62 +910,58 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102353836</t>
+          <t>https://artportalen.se/Sighting/101972023</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101960910</v>
+        <v>102353836</v>
       </c>
       <c r="B4" t="n">
-        <v>5257</v>
+        <v>40267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101424</v>
+        <v>101166</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulröd blankbock</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Obrium cantharinum</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>puppa</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Hultet, Sm</t>
@@ -1040,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1055,7 +1018,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flög runt, och kröp på, färska timmerhögar med framförallt grov gran men med visst inslag av asp</t>
+          <t>På grov asp-stam i timmerhög. Den yttersta delen av puppan stack ut ur kläckhålet (uttagen på bilden). Fyra ex av grön aspvedbock sprang runt på samma stam.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1082,16 +1045,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101960910</t>
+          <t>https://artportalen.se/Sighting/102353836</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101984142</v>
+        <v>101960910</v>
       </c>
       <c r="B5" t="n">
-        <v>57754</v>
+        <v>5257</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,21 +1062,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102118</v>
+        <v>101424</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Gulröd blankbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Obrium cantharinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1121,14 +1084,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Hultet, Sm</t>
@@ -1170,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1183,12 +1155,18 @@
           <t>03:00</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flög runt, och kröp på, färska timmerhögar med framförallt grov gran men med visst inslag av asp</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1206,62 +1184,53 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101984142</t>
+          <t>https://artportalen.se/Sighting/101960910</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101972020</v>
+        <v>101984142</v>
       </c>
       <c r="B6" t="n">
-        <v>8825</v>
+        <v>57754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102341</v>
+        <v>102118</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jätteknäppare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Stenagostus rufus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(De Geer, 1774)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Hultet, Sm</t>
@@ -1322,7 +1291,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1339,6 +1307,140 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101984142</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>101972020</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8825</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102341</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jätteknäppare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Stenagostus rufus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(De Geer, 1774)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>S Hultet, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>578783</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6337436</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl, Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/101972020</t>
         </is>
@@ -1351,6 +1453,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92353</v>
+        <v>92355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92355</v>
+        <v>92368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92368</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158491</v>
       </c>
       <c r="B2" t="n">
-        <v>92410</v>
+        <v>92414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
